--- a/AAII_Financials/Quarterly/FVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FVI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>FVI</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>334400</v>
+        <v>359000</v>
       </c>
       <c r="E8" s="3">
-        <v>217900</v>
+        <v>329000</v>
       </c>
       <c r="F8" s="3">
-        <v>241700</v>
+        <v>214300</v>
       </c>
       <c r="G8" s="3">
-        <v>226500</v>
+        <v>237800</v>
       </c>
       <c r="H8" s="3">
-        <v>229200</v>
+        <v>222900</v>
       </c>
       <c r="I8" s="3">
-        <v>230900</v>
+        <v>225400</v>
       </c>
       <c r="J8" s="3">
+        <v>227200</v>
+      </c>
+      <c r="K8" s="3">
         <v>250800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>268700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>219500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>166600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>162900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>133800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>108800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>56700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>60500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>88500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>243700</v>
+        <v>267000</v>
       </c>
       <c r="E9" s="3">
-        <v>173900</v>
+        <v>239800</v>
       </c>
       <c r="F9" s="3">
-        <v>186000</v>
+        <v>171000</v>
       </c>
       <c r="G9" s="3">
-        <v>185500</v>
+        <v>183000</v>
       </c>
       <c r="H9" s="3">
-        <v>193700</v>
+        <v>182500</v>
       </c>
       <c r="I9" s="3">
-        <v>180600</v>
+        <v>190500</v>
       </c>
       <c r="J9" s="3">
+        <v>177700</v>
+      </c>
+      <c r="K9" s="3">
         <v>163400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>182700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>153100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>99600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>92100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>73100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>54000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>51200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>56700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>90700</v>
+        <v>92000</v>
       </c>
       <c r="E10" s="3">
-        <v>44000</v>
+        <v>89200</v>
       </c>
       <c r="F10" s="3">
-        <v>55600</v>
+        <v>43300</v>
       </c>
       <c r="G10" s="3">
-        <v>41000</v>
+        <v>54700</v>
       </c>
       <c r="H10" s="3">
-        <v>35500</v>
+        <v>40400</v>
       </c>
       <c r="I10" s="3">
-        <v>50400</v>
+        <v>34900</v>
       </c>
       <c r="J10" s="3">
+        <v>49500</v>
+      </c>
+      <c r="K10" s="3">
         <v>87300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>86000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>66400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>70800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>54800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,37 +945,38 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="3">
-        <v>800</v>
+      <c r="E12" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="F12" s="3">
+        <v>700</v>
+      </c>
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="I12" s="3">
-        <v>700</v>
       </c>
       <c r="J12" s="3">
         <v>700</v>
       </c>
       <c r="K12" s="3">
+        <v>700</v>
+      </c>
+      <c r="L12" s="3">
         <v>600</v>
-      </c>
-      <c r="L12" s="3">
-        <v>300</v>
       </c>
       <c r="M12" s="3">
         <v>300</v>
@@ -972,25 +985,28 @@
         <v>300</v>
       </c>
       <c r="O12" s="3">
+        <v>300</v>
+      </c>
+      <c r="P12" s="3">
         <v>700</v>
-      </c>
-      <c r="P12" s="3">
-        <v>200</v>
       </c>
       <c r="Q12" s="3">
         <v>200</v>
       </c>
       <c r="R12" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="S12" s="3">
         <v>500</v>
       </c>
       <c r="T12" s="3">
+        <v>500</v>
+      </c>
+      <c r="U12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,64 +1061,70 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>151600</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
-        <v>257200</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>6100</v>
+        <v>253100</v>
       </c>
       <c r="I14" s="3">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="J14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>17100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>271900</v>
+        <v>463700</v>
       </c>
       <c r="E17" s="3">
-        <v>207300</v>
+        <v>267500</v>
       </c>
       <c r="F17" s="3">
-        <v>208800</v>
+        <v>203900</v>
       </c>
       <c r="G17" s="3">
-        <v>464700</v>
+        <v>205400</v>
       </c>
       <c r="H17" s="3">
-        <v>221300</v>
+        <v>457200</v>
       </c>
       <c r="I17" s="3">
-        <v>212800</v>
+        <v>217700</v>
       </c>
       <c r="J17" s="3">
+        <v>209400</v>
+      </c>
+      <c r="K17" s="3">
         <v>194800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>217000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>204300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>122000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>107100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>97300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>71700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>58200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>80500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>62500</v>
+        <v>-104700</v>
       </c>
       <c r="E18" s="3">
-        <v>10600</v>
+        <v>61500</v>
       </c>
       <c r="F18" s="3">
-        <v>32900</v>
+        <v>10400</v>
       </c>
       <c r="G18" s="3">
-        <v>-238100</v>
+        <v>32400</v>
       </c>
       <c r="H18" s="3">
-        <v>7900</v>
+        <v>-234300</v>
       </c>
       <c r="I18" s="3">
-        <v>18100</v>
+        <v>7800</v>
       </c>
       <c r="J18" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K18" s="3">
         <v>56000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>51600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>44700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1310,288 +1342,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-9400</v>
+        <v>7600</v>
       </c>
       <c r="E20" s="3">
-        <v>-3100</v>
+        <v>-9300</v>
       </c>
       <c r="F20" s="3">
-        <v>-4800</v>
+        <v>-3000</v>
       </c>
       <c r="G20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-5500</v>
-      </c>
       <c r="I20" s="3">
-        <v>3700</v>
+        <v>-5400</v>
       </c>
       <c r="J20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-8700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>141000</v>
+        <v>-200</v>
       </c>
       <c r="E21" s="3">
-        <v>62500</v>
+        <v>138700</v>
       </c>
       <c r="F21" s="3">
-        <v>89000</v>
+        <v>61400</v>
       </c>
       <c r="G21" s="3">
-        <v>-179000</v>
+        <v>87500</v>
       </c>
       <c r="H21" s="3">
-        <v>66800</v>
+        <v>-176000</v>
       </c>
       <c r="I21" s="3">
-        <v>80900</v>
+        <v>65800</v>
       </c>
       <c r="J21" s="3">
+        <v>79600</v>
+      </c>
+      <c r="K21" s="3">
         <v>100200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>105900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>67300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>69700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>84400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>51200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>800</v>
       </c>
       <c r="J22" s="3">
         <v>800</v>
       </c>
       <c r="K22" s="3">
+        <v>800</v>
+      </c>
+      <c r="L22" s="3">
         <v>4600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
-      </c>
-      <c r="P22" s="3">
-        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
       </c>
       <c r="R22" s="3">
+        <v>200</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>51500</v>
+        <v>-98500</v>
       </c>
       <c r="E23" s="3">
-        <v>6200</v>
+        <v>50700</v>
       </c>
       <c r="F23" s="3">
-        <v>27200</v>
+        <v>6100</v>
       </c>
       <c r="G23" s="3">
-        <v>-241800</v>
+        <v>26800</v>
       </c>
       <c r="H23" s="3">
+        <v>-237800</v>
+      </c>
+      <c r="I23" s="3">
         <v>2200</v>
       </c>
-      <c r="I23" s="3">
-        <v>21000</v>
-      </c>
       <c r="J23" s="3">
+        <v>20700</v>
+      </c>
+      <c r="K23" s="3">
         <v>46400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>40800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>39000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>54900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>35800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>25700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="I24" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K24" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="M24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>16700</v>
+      </c>
+      <c r="O24" s="3">
+        <v>18400</v>
+      </c>
+      <c r="P24" s="3">
+        <v>11800</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>19500</v>
+      </c>
+      <c r="R24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S24" s="3">
         <v>9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
-        <v>10900</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="U24" s="3">
         <v>7900</v>
       </c>
-      <c r="I24" s="3">
-        <v>18700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>9300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>18300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>12000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>16700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>18400</v>
-      </c>
-      <c r="O24" s="3">
-        <v>11800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>19500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="T24" s="3">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>42500</v>
+        <v>-121600</v>
       </c>
       <c r="E26" s="3">
-        <v>4800</v>
+        <v>41800</v>
       </c>
       <c r="F26" s="3">
-        <v>16300</v>
+        <v>4700</v>
       </c>
       <c r="G26" s="3">
-        <v>-220700</v>
+        <v>16000</v>
       </c>
       <c r="H26" s="3">
+        <v>-217100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K26" s="3">
+        <v>37100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>22400</v>
+      </c>
+      <c r="M26" s="3">
+        <v>300</v>
+      </c>
+      <c r="N26" s="3">
+        <v>22400</v>
+      </c>
+      <c r="O26" s="3">
+        <v>36500</v>
+      </c>
+      <c r="P26" s="3">
+        <v>24100</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>17100</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="S26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>37100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>22400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>22400</v>
-      </c>
-      <c r="N26" s="3">
-        <v>36500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>24100</v>
-      </c>
-      <c r="P26" s="3">
-        <v>17100</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>37800</v>
+        <v>-124900</v>
       </c>
       <c r="E27" s="3">
-        <v>4300</v>
+        <v>37200</v>
       </c>
       <c r="F27" s="3">
-        <v>15000</v>
+        <v>4200</v>
       </c>
       <c r="G27" s="3">
-        <v>-210100</v>
+        <v>14700</v>
       </c>
       <c r="H27" s="3">
-        <v>-5200</v>
+        <v>-206700</v>
       </c>
       <c r="I27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J27" s="3">
         <v>3200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>35900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1982,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>9400</v>
+        <v>-7600</v>
       </c>
       <c r="E32" s="3">
-        <v>3100</v>
+        <v>9300</v>
       </c>
       <c r="F32" s="3">
-        <v>4800</v>
+        <v>3000</v>
       </c>
       <c r="G32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
-        <v>5500</v>
-      </c>
       <c r="I32" s="3">
-        <v>-3700</v>
+        <v>5400</v>
       </c>
       <c r="J32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="K32" s="3">
         <v>8700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>37800</v>
+        <v>-124900</v>
       </c>
       <c r="E33" s="3">
-        <v>4300</v>
+        <v>37200</v>
       </c>
       <c r="F33" s="3">
-        <v>15000</v>
+        <v>4200</v>
       </c>
       <c r="G33" s="3">
-        <v>-210100</v>
+        <v>14700</v>
       </c>
       <c r="H33" s="3">
-        <v>-5200</v>
+        <v>-206700</v>
       </c>
       <c r="I33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J33" s="3">
         <v>3200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>35900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>37800</v>
+        <v>-124900</v>
       </c>
       <c r="E35" s="3">
-        <v>4300</v>
+        <v>37200</v>
       </c>
       <c r="F35" s="3">
-        <v>15000</v>
+        <v>4200</v>
       </c>
       <c r="G35" s="3">
-        <v>-210100</v>
+        <v>14700</v>
       </c>
       <c r="H35" s="3">
-        <v>-5200</v>
+        <v>-206700</v>
       </c>
       <c r="I35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J35" s="3">
         <v>3200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>35900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2311,64 +2396,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>162000</v>
+        <v>173400</v>
       </c>
       <c r="E41" s="3">
-        <v>128500</v>
+        <v>159400</v>
       </c>
       <c r="F41" s="3">
-        <v>116500</v>
+        <v>126400</v>
       </c>
       <c r="G41" s="3">
-        <v>110700</v>
+        <v>114700</v>
       </c>
       <c r="H41" s="3">
-        <v>125100</v>
+        <v>108900</v>
       </c>
       <c r="I41" s="3">
-        <v>159700</v>
+        <v>123000</v>
       </c>
       <c r="J41" s="3">
+        <v>157100</v>
+      </c>
+      <c r="K41" s="3">
         <v>151800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>144700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>183300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>168400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>201400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>170500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>111100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>97700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>112800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>107000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2381,32 +2470,32 @@
       <c r="F42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G42" s="3">
-        <v>100</v>
+      <c r="G42" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H42" s="3">
         <v>100</v>
       </c>
       <c r="I42" s="3">
+        <v>100</v>
+      </c>
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1200</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>35</v>
@@ -2417,350 +2506,371 @@
       <c r="R42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>94800</v>
+        <v>101000</v>
       </c>
       <c r="E43" s="3">
-        <v>93300</v>
+        <v>93200</v>
       </c>
       <c r="F43" s="3">
-        <v>109100</v>
+        <v>91800</v>
       </c>
       <c r="G43" s="3">
-        <v>94700</v>
+        <v>107400</v>
       </c>
       <c r="H43" s="3">
-        <v>90400</v>
+        <v>93200</v>
       </c>
       <c r="I43" s="3">
-        <v>102300</v>
+        <v>88900</v>
       </c>
       <c r="J43" s="3">
+        <v>100600</v>
+      </c>
+      <c r="K43" s="3">
         <v>123700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>105600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>93100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>107800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>98900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>43300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>61200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>182600</v>
+        <v>156700</v>
       </c>
       <c r="E44" s="3">
-        <v>144500</v>
+        <v>179600</v>
       </c>
       <c r="F44" s="3">
-        <v>123600</v>
+        <v>142200</v>
       </c>
       <c r="G44" s="3">
-        <v>126600</v>
+        <v>121600</v>
       </c>
       <c r="H44" s="3">
-        <v>113800</v>
+        <v>124500</v>
       </c>
       <c r="I44" s="3">
-        <v>118600</v>
+        <v>111900</v>
       </c>
       <c r="J44" s="3">
+        <v>116600</v>
+      </c>
+      <c r="K44" s="3">
         <v>125600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>115900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>96300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>72800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>45600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>16500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>17000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14900</v>
+        <v>19900</v>
       </c>
       <c r="E45" s="3">
-        <v>11900</v>
+        <v>14700</v>
       </c>
       <c r="F45" s="3">
-        <v>14900</v>
+        <v>11700</v>
       </c>
       <c r="G45" s="3">
-        <v>15400</v>
+        <v>14700</v>
       </c>
       <c r="H45" s="3">
-        <v>17100</v>
+        <v>15200</v>
       </c>
       <c r="I45" s="3">
-        <v>14900</v>
+        <v>16800</v>
       </c>
       <c r="J45" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K45" s="3">
         <v>13100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>454300</v>
+        <v>451100</v>
       </c>
       <c r="E46" s="3">
-        <v>378300</v>
+        <v>446900</v>
       </c>
       <c r="F46" s="3">
-        <v>364200</v>
+        <v>372100</v>
       </c>
       <c r="G46" s="3">
-        <v>347600</v>
+        <v>358300</v>
       </c>
       <c r="H46" s="3">
-        <v>346400</v>
+        <v>342000</v>
       </c>
       <c r="I46" s="3">
-        <v>395800</v>
+        <v>340800</v>
       </c>
       <c r="J46" s="3">
+        <v>389400</v>
+      </c>
+      <c r="K46" s="3">
         <v>414700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>379700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>389900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>353400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>388000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>320600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>182500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>168800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>181000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>195100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>162300</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11600</v>
+        <v>19400</v>
       </c>
       <c r="E47" s="3">
-        <v>20000</v>
+        <v>11400</v>
       </c>
       <c r="F47" s="3">
-        <v>6900</v>
+        <v>19700</v>
       </c>
       <c r="G47" s="3">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="H47" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J47" s="3">
         <v>6300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L47" s="3">
+        <v>6100</v>
+      </c>
+      <c r="M47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="N47" s="3">
+        <v>55300</v>
+      </c>
+      <c r="O47" s="3">
         <v>6400</v>
       </c>
-      <c r="J47" s="3">
-        <v>6500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>6100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>24000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>55300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>6400</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>61100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>63700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>66000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>66600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>62800</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2284500</v>
+        <v>2130200</v>
       </c>
       <c r="E48" s="3">
-        <v>2274200</v>
+        <v>2247500</v>
       </c>
       <c r="F48" s="3">
-        <v>2239200</v>
+        <v>2237300</v>
       </c>
       <c r="G48" s="3">
-        <v>2156300</v>
+        <v>2202900</v>
       </c>
       <c r="H48" s="3">
-        <v>2380300</v>
+        <v>2121300</v>
       </c>
       <c r="I48" s="3">
-        <v>2377600</v>
+        <v>2341700</v>
       </c>
       <c r="J48" s="3">
+        <v>2339100</v>
+      </c>
+      <c r="K48" s="3">
         <v>2364800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2312900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2244400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1068000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1077700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1022500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1045000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>990100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>973400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>938900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>892600</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,49 +3043,52 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>64700</v>
+        <v>62200</v>
       </c>
       <c r="E52" s="3">
-        <v>66900</v>
+        <v>63600</v>
       </c>
       <c r="F52" s="3">
-        <v>66400</v>
+        <v>65800</v>
       </c>
       <c r="G52" s="3">
-        <v>70300</v>
+        <v>65300</v>
       </c>
       <c r="H52" s="3">
-        <v>62900</v>
+        <v>69200</v>
       </c>
       <c r="I52" s="3">
-        <v>53700</v>
+        <v>61900</v>
       </c>
       <c r="J52" s="3">
+        <v>52800</v>
+      </c>
+      <c r="K52" s="3">
         <v>48100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19700</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>35</v>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2815100</v>
+        <v>2662900</v>
       </c>
       <c r="E54" s="3">
-        <v>2739300</v>
+        <v>2769400</v>
       </c>
       <c r="F54" s="3">
-        <v>2676800</v>
+        <v>2694900</v>
       </c>
       <c r="G54" s="3">
-        <v>2580700</v>
+        <v>2633400</v>
       </c>
       <c r="H54" s="3">
-        <v>2795900</v>
+        <v>2538900</v>
       </c>
       <c r="I54" s="3">
-        <v>2833500</v>
+        <v>2750600</v>
       </c>
       <c r="J54" s="3">
+        <v>2787600</v>
+      </c>
+      <c r="K54" s="3">
         <v>2834100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2731000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2702900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1497700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1478200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1363900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1288500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1222500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1220500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1200600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1117800</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,344 +3268,363 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>107800</v>
+        <v>135800</v>
       </c>
       <c r="E57" s="3">
+        <v>106000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>100500</v>
+      </c>
+      <c r="G57" s="3">
         <v>102200</v>
       </c>
-      <c r="F57" s="3">
-        <v>103800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>99800</v>
-      </c>
       <c r="H57" s="3">
-        <v>98400</v>
+        <v>98200</v>
       </c>
       <c r="I57" s="3">
-        <v>92800</v>
+        <v>96800</v>
       </c>
       <c r="J57" s="3">
+        <v>91300</v>
+      </c>
+      <c r="K57" s="3">
         <v>100300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>111500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>114200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>36700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>52600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17600</v>
+        <v>79600</v>
       </c>
       <c r="E58" s="3">
-        <v>21500</v>
+        <v>17300</v>
       </c>
       <c r="F58" s="3">
-        <v>18200</v>
+        <v>21100</v>
       </c>
       <c r="G58" s="3">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="H58" s="3">
-        <v>14200</v>
+        <v>12700</v>
       </c>
       <c r="I58" s="3">
-        <v>14100</v>
+        <v>13900</v>
       </c>
       <c r="J58" s="3">
-        <v>14200</v>
+        <v>13900</v>
       </c>
       <c r="K58" s="3">
         <v>14200</v>
       </c>
       <c r="L58" s="3">
+        <v>14200</v>
+      </c>
+      <c r="M58" s="3">
         <v>208500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>172500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>174400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>49000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>89000</v>
+        <v>114400</v>
       </c>
       <c r="E59" s="3">
-        <v>67100</v>
+        <v>87500</v>
       </c>
       <c r="F59" s="3">
-        <v>69300</v>
+        <v>66000</v>
       </c>
       <c r="G59" s="3">
-        <v>73000</v>
+        <v>68200</v>
       </c>
       <c r="H59" s="3">
-        <v>67300</v>
+        <v>71800</v>
       </c>
       <c r="I59" s="3">
-        <v>68000</v>
+        <v>66200</v>
       </c>
       <c r="J59" s="3">
+        <v>66900</v>
+      </c>
+      <c r="K59" s="3">
         <v>85700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>99600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>82100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>65600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>61400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>38700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>51300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>214400</v>
+        <v>329900</v>
       </c>
       <c r="E60" s="3">
-        <v>190700</v>
+        <v>210900</v>
       </c>
       <c r="F60" s="3">
-        <v>191400</v>
+        <v>187600</v>
       </c>
       <c r="G60" s="3">
-        <v>185800</v>
+        <v>188300</v>
       </c>
       <c r="H60" s="3">
-        <v>179900</v>
+        <v>182800</v>
       </c>
       <c r="I60" s="3">
-        <v>175000</v>
+        <v>176900</v>
       </c>
       <c r="J60" s="3">
+        <v>172200</v>
+      </c>
+      <c r="K60" s="3">
         <v>200200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>225300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>404900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>282000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>285900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>124600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>105500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>85700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>133100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>115100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>103300</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>394700</v>
+        <v>278000</v>
       </c>
       <c r="E61" s="3">
-        <v>444600</v>
+        <v>388300</v>
       </c>
       <c r="F61" s="3">
-        <v>388900</v>
+        <v>437400</v>
       </c>
       <c r="G61" s="3">
-        <v>317900</v>
+        <v>382600</v>
       </c>
       <c r="H61" s="3">
-        <v>299800</v>
+        <v>312700</v>
       </c>
       <c r="I61" s="3">
-        <v>321400</v>
+        <v>294900</v>
       </c>
       <c r="J61" s="3">
+        <v>316200</v>
+      </c>
+      <c r="K61" s="3">
         <v>295900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>238200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>87300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>71100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>71300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>221200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>190700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>185200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>217500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>207200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>306600</v>
+        <v>312000</v>
       </c>
       <c r="E62" s="3">
-        <v>308300</v>
+        <v>301600</v>
       </c>
       <c r="F62" s="3">
-        <v>308000</v>
+        <v>303300</v>
       </c>
       <c r="G62" s="3">
-        <v>304500</v>
+        <v>303000</v>
       </c>
       <c r="H62" s="3">
-        <v>335700</v>
+        <v>299500</v>
       </c>
       <c r="I62" s="3">
-        <v>339600</v>
+        <v>330200</v>
       </c>
       <c r="J62" s="3">
+        <v>334100</v>
+      </c>
+      <c r="K62" s="3">
         <v>335000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>336600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>302100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>80100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>70500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>69900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>65900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>63200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>69800</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>980700</v>
+        <v>987200</v>
       </c>
       <c r="E66" s="3">
-        <v>1005900</v>
+        <v>964800</v>
       </c>
       <c r="F66" s="3">
-        <v>950100</v>
+        <v>989600</v>
       </c>
       <c r="G66" s="3">
-        <v>868600</v>
+        <v>934700</v>
       </c>
       <c r="H66" s="3">
-        <v>886300</v>
+        <v>854500</v>
       </c>
       <c r="I66" s="3">
-        <v>911300</v>
+        <v>871900</v>
       </c>
       <c r="J66" s="3">
+        <v>896500</v>
+      </c>
+      <c r="K66" s="3">
         <v>907200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>873600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>866400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>432400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>437200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>425900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>366600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>340700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>416500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>385600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>283500</v>
+        <v>152600</v>
       </c>
       <c r="E72" s="3">
-        <v>244700</v>
+        <v>279000</v>
       </c>
       <c r="F72" s="3">
-        <v>242300</v>
+        <v>240800</v>
       </c>
       <c r="G72" s="3">
-        <v>228800</v>
+        <v>238400</v>
       </c>
       <c r="H72" s="3">
-        <v>438400</v>
+        <v>225100</v>
       </c>
       <c r="I72" s="3">
-        <v>442000</v>
+        <v>431300</v>
       </c>
       <c r="J72" s="3">
+        <v>434900</v>
+      </c>
+      <c r="K72" s="3">
         <v>438800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>396200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>374300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>370600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>347500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>301700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>279700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>256000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>263400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>273600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>241300</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1834400</v>
+        <v>1675800</v>
       </c>
       <c r="E76" s="3">
-        <v>1733400</v>
+        <v>1804600</v>
       </c>
       <c r="F76" s="3">
-        <v>1726700</v>
+        <v>1705300</v>
       </c>
       <c r="G76" s="3">
-        <v>1712200</v>
+        <v>1698700</v>
       </c>
       <c r="H76" s="3">
-        <v>1909600</v>
+        <v>1684400</v>
       </c>
       <c r="I76" s="3">
-        <v>1922200</v>
+        <v>1878600</v>
       </c>
       <c r="J76" s="3">
+        <v>1891100</v>
+      </c>
+      <c r="K76" s="3">
         <v>1926800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1857400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1836500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1065400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1041000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>938000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>921900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>881800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>803900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>815000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>782700</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>37800</v>
+        <v>-124900</v>
       </c>
       <c r="E81" s="3">
-        <v>4300</v>
+        <v>37200</v>
       </c>
       <c r="F81" s="3">
-        <v>15000</v>
+        <v>4200</v>
       </c>
       <c r="G81" s="3">
-        <v>-210100</v>
+        <v>14700</v>
       </c>
       <c r="H81" s="3">
-        <v>-5200</v>
+        <v>-206700</v>
       </c>
       <c r="I81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J81" s="3">
         <v>3200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>35900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4617,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>87900</v>
+        <v>96900</v>
       </c>
       <c r="E83" s="3">
-        <v>54900</v>
+        <v>86500</v>
       </c>
       <c r="F83" s="3">
-        <v>60800</v>
+        <v>54000</v>
       </c>
       <c r="G83" s="3">
-        <v>61200</v>
+        <v>59900</v>
       </c>
       <c r="H83" s="3">
-        <v>64500</v>
+        <v>60200</v>
       </c>
       <c r="I83" s="3">
-        <v>59100</v>
+        <v>63400</v>
       </c>
       <c r="J83" s="3">
+        <v>58100</v>
+      </c>
+      <c r="K83" s="3">
         <v>53000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>60500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>28400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>146400</v>
+        <v>142200</v>
       </c>
       <c r="E89" s="3">
-        <v>60000</v>
+        <v>144100</v>
       </c>
       <c r="F89" s="3">
-        <v>57400</v>
+        <v>59000</v>
       </c>
       <c r="G89" s="3">
-        <v>68300</v>
+        <v>56500</v>
       </c>
       <c r="H89" s="3">
-        <v>88900</v>
+        <v>67100</v>
       </c>
       <c r="I89" s="3">
-        <v>64300</v>
+        <v>87500</v>
       </c>
       <c r="J89" s="3">
+        <v>63200</v>
+      </c>
+      <c r="K89" s="3">
         <v>45700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>77100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>53200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>59300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-73300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-54000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-62100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-53800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-500</v>
       </c>
       <c r="P91" s="3">
         <v>-500</v>
       </c>
       <c r="Q91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-46300</v>
+        <v>-69000</v>
       </c>
       <c r="E94" s="3">
-        <v>-99900</v>
+        <v>-45600</v>
       </c>
       <c r="F94" s="3">
-        <v>-82000</v>
+        <v>-98300</v>
       </c>
       <c r="G94" s="3">
-        <v>-100200</v>
+        <v>-80600</v>
       </c>
       <c r="H94" s="3">
-        <v>-81100</v>
+        <v>-98500</v>
       </c>
       <c r="I94" s="3">
-        <v>-79900</v>
+        <v>-79800</v>
       </c>
       <c r="J94" s="3">
+        <v>-78600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-90100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-69200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-70100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-46900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-58700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-80100</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5546,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-64800</v>
+        <v>-61200</v>
       </c>
       <c r="E100" s="3">
-        <v>51800</v>
+        <v>-63800</v>
       </c>
       <c r="F100" s="3">
-        <v>30300</v>
+        <v>51000</v>
       </c>
       <c r="G100" s="3">
-        <v>15600</v>
+        <v>29800</v>
       </c>
       <c r="H100" s="3">
-        <v>-32500</v>
+        <v>15300</v>
       </c>
       <c r="I100" s="3">
-        <v>19300</v>
+        <v>-32000</v>
       </c>
       <c r="J100" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K100" s="3">
         <v>50600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-46600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>29100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>48800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>52900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1800</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
-        <v>-10000</v>
-      </c>
       <c r="I101" s="3">
-        <v>4300</v>
+        <v>-9800</v>
       </c>
       <c r="J101" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>-100</v>
       </c>
       <c r="S101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T101" s="3">
         <v>-2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>33500</v>
+        <v>14000</v>
       </c>
       <c r="E102" s="3">
-        <v>12000</v>
+        <v>33000</v>
       </c>
       <c r="F102" s="3">
-        <v>5800</v>
+        <v>11800</v>
       </c>
       <c r="G102" s="3">
-        <v>-14300</v>
+        <v>5700</v>
       </c>
       <c r="H102" s="3">
-        <v>-34700</v>
+        <v>-14100</v>
       </c>
       <c r="I102" s="3">
-        <v>7900</v>
+        <v>-34100</v>
       </c>
       <c r="J102" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K102" s="3">
         <v>4500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>60400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>FVI</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>359000</v>
+        <v>308600</v>
       </c>
       <c r="E8" s="3">
-        <v>329000</v>
+        <v>364000</v>
       </c>
       <c r="F8" s="3">
-        <v>214300</v>
+        <v>333600</v>
       </c>
       <c r="G8" s="3">
-        <v>237800</v>
+        <v>217400</v>
       </c>
       <c r="H8" s="3">
-        <v>222900</v>
+        <v>241100</v>
       </c>
       <c r="I8" s="3">
-        <v>225400</v>
+        <v>226000</v>
       </c>
       <c r="J8" s="3">
+        <v>228600</v>
+      </c>
+      <c r="K8" s="3">
         <v>227200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>250800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>268700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>219500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>166600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>162900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>133800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>108800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>56700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>60500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>88500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>267000</v>
+        <v>212700</v>
       </c>
       <c r="E9" s="3">
-        <v>239800</v>
+        <v>270700</v>
       </c>
       <c r="F9" s="3">
-        <v>171000</v>
+        <v>243100</v>
       </c>
       <c r="G9" s="3">
-        <v>183000</v>
+        <v>173400</v>
       </c>
       <c r="H9" s="3">
-        <v>182500</v>
+        <v>185600</v>
       </c>
       <c r="I9" s="3">
-        <v>190500</v>
+        <v>185100</v>
       </c>
       <c r="J9" s="3">
+        <v>193200</v>
+      </c>
+      <c r="K9" s="3">
         <v>177700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>163400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>182700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>153100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>99600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>92100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>73100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>54000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>39000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>51200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>56700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>92000</v>
+        <v>95900</v>
       </c>
       <c r="E10" s="3">
-        <v>89200</v>
+        <v>93300</v>
       </c>
       <c r="F10" s="3">
-        <v>43300</v>
+        <v>90400</v>
       </c>
       <c r="G10" s="3">
-        <v>54700</v>
+        <v>43900</v>
       </c>
       <c r="H10" s="3">
-        <v>40400</v>
+        <v>55500</v>
       </c>
       <c r="I10" s="3">
-        <v>34900</v>
+        <v>40900</v>
       </c>
       <c r="J10" s="3">
+        <v>35400</v>
+      </c>
+      <c r="K10" s="3">
         <v>49500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>87300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>67000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>70800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>54800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,29 +971,29 @@
       <c r="E12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="3">
-        <v>700</v>
+      <c r="F12" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="G12" s="3">
+        <v>800</v>
+      </c>
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="J12" s="3">
-        <v>700</v>
       </c>
       <c r="K12" s="3">
         <v>700</v>
       </c>
       <c r="L12" s="3">
+        <v>700</v>
+      </c>
+      <c r="M12" s="3">
         <v>600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>300</v>
       </c>
       <c r="N12" s="3">
         <v>300</v>
@@ -988,25 +1002,28 @@
         <v>300</v>
       </c>
       <c r="P12" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q12" s="3">
         <v>700</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>200</v>
       </c>
       <c r="R12" s="3">
         <v>200</v>
       </c>
       <c r="S12" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="T12" s="3">
         <v>500</v>
       </c>
       <c r="U12" s="3">
+        <v>500</v>
+      </c>
+      <c r="V12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1064,67 +1081,73 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>151600</v>
+      <c r="D14" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E14" s="3">
+        <v>153800</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
-        <v>253100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>6000</v>
+        <v>256600</v>
       </c>
       <c r="J14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K14" s="3">
         <v>5500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>17100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>463700</v>
+        <v>244000</v>
       </c>
       <c r="E17" s="3">
-        <v>267500</v>
+        <v>470200</v>
       </c>
       <c r="F17" s="3">
-        <v>203900</v>
+        <v>271200</v>
       </c>
       <c r="G17" s="3">
-        <v>205400</v>
+        <v>206800</v>
       </c>
       <c r="H17" s="3">
-        <v>457200</v>
+        <v>208300</v>
       </c>
       <c r="I17" s="3">
-        <v>217700</v>
+        <v>463600</v>
       </c>
       <c r="J17" s="3">
+        <v>220700</v>
+      </c>
+      <c r="K17" s="3">
         <v>209400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>194800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>217000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>204300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>107100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>97300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>71700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>58300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>76900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>80500</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-104700</v>
+        <v>64600</v>
       </c>
       <c r="E18" s="3">
-        <v>61500</v>
+        <v>-106200</v>
       </c>
       <c r="F18" s="3">
-        <v>10400</v>
+        <v>62300</v>
       </c>
       <c r="G18" s="3">
-        <v>32400</v>
+        <v>10600</v>
       </c>
       <c r="H18" s="3">
-        <v>-234300</v>
+        <v>32800</v>
       </c>
       <c r="I18" s="3">
-        <v>7800</v>
+        <v>-237600</v>
       </c>
       <c r="J18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K18" s="3">
         <v>17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>44700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>55800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1343,303 +1376,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>7600</v>
+        <v>3200</v>
       </c>
       <c r="E20" s="3">
-        <v>-9300</v>
+        <v>7700</v>
       </c>
       <c r="F20" s="3">
-        <v>-3000</v>
+        <v>-9400</v>
       </c>
       <c r="G20" s="3">
-        <v>-4700</v>
+        <v>-3100</v>
       </c>
       <c r="H20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
-        <v>-5400</v>
-      </c>
       <c r="J20" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>14300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
-        <v>138700</v>
-      </c>
       <c r="F21" s="3">
-        <v>61400</v>
+        <v>140600</v>
       </c>
       <c r="G21" s="3">
-        <v>87500</v>
+        <v>62300</v>
       </c>
       <c r="H21" s="3">
-        <v>-176000</v>
+        <v>88800</v>
       </c>
       <c r="I21" s="3">
-        <v>65800</v>
+        <v>-178500</v>
       </c>
       <c r="J21" s="3">
+        <v>66700</v>
+      </c>
+      <c r="K21" s="3">
         <v>79600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>100200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>105900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>67300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>69700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>84400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>54900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>51200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>40800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>800</v>
       </c>
       <c r="L22" s="3">
+        <v>800</v>
+      </c>
+      <c r="M22" s="3">
         <v>4600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
       </c>
       <c r="S22" s="3">
+        <v>200</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-98500</v>
+        <v>59800</v>
       </c>
       <c r="E23" s="3">
-        <v>50700</v>
+        <v>-99900</v>
       </c>
       <c r="F23" s="3">
-        <v>6100</v>
+        <v>51400</v>
       </c>
       <c r="G23" s="3">
-        <v>26800</v>
+        <v>6200</v>
       </c>
       <c r="H23" s="3">
-        <v>-237800</v>
+        <v>27200</v>
       </c>
       <c r="I23" s="3">
+        <v>-241200</v>
+      </c>
+      <c r="J23" s="3">
         <v>2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>40800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>39000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>54900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>35800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>25700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>23000</v>
+        <v>19900</v>
       </c>
       <c r="E24" s="3">
-        <v>8900</v>
+        <v>23400</v>
       </c>
       <c r="F24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="G24" s="3">
-        <v>10700</v>
-      </c>
       <c r="H24" s="3">
-        <v>-20700</v>
+        <v>10900</v>
       </c>
       <c r="I24" s="3">
-        <v>7800</v>
+        <v>-21000</v>
       </c>
       <c r="J24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K24" s="3">
         <v>18400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>18300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-121600</v>
+        <v>39900</v>
       </c>
       <c r="E26" s="3">
-        <v>41800</v>
+        <v>-123300</v>
       </c>
       <c r="F26" s="3">
-        <v>4700</v>
+        <v>42400</v>
       </c>
       <c r="G26" s="3">
-        <v>16000</v>
+        <v>4800</v>
       </c>
       <c r="H26" s="3">
-        <v>-217100</v>
+        <v>16300</v>
       </c>
       <c r="I26" s="3">
-        <v>-5600</v>
+        <v>-220100</v>
       </c>
       <c r="J26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>22400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>22400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-124900</v>
+        <v>36000</v>
       </c>
       <c r="E27" s="3">
-        <v>37200</v>
+        <v>-126700</v>
       </c>
       <c r="F27" s="3">
-        <v>4200</v>
+        <v>37700</v>
       </c>
       <c r="G27" s="3">
-        <v>14700</v>
+        <v>4300</v>
       </c>
       <c r="H27" s="3">
-        <v>-206700</v>
+        <v>14900</v>
       </c>
       <c r="I27" s="3">
-        <v>-5100</v>
+        <v>-209600</v>
       </c>
       <c r="J27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K27" s="3">
         <v>3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>35900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>36500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-7600</v>
+        <v>-3200</v>
       </c>
       <c r="E32" s="3">
-        <v>9300</v>
+        <v>-7700</v>
       </c>
       <c r="F32" s="3">
-        <v>3000</v>
+        <v>9400</v>
       </c>
       <c r="G32" s="3">
-        <v>4700</v>
+        <v>3100</v>
       </c>
       <c r="H32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
-        <v>5400</v>
-      </c>
       <c r="J32" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-14300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-124900</v>
+        <v>36000</v>
       </c>
       <c r="E33" s="3">
-        <v>37200</v>
+        <v>-126700</v>
       </c>
       <c r="F33" s="3">
-        <v>4200</v>
+        <v>37700</v>
       </c>
       <c r="G33" s="3">
-        <v>14700</v>
+        <v>4300</v>
       </c>
       <c r="H33" s="3">
-        <v>-206700</v>
+        <v>14900</v>
       </c>
       <c r="I33" s="3">
-        <v>-5100</v>
+        <v>-209600</v>
       </c>
       <c r="J33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K33" s="3">
         <v>3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>36500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-124900</v>
+        <v>36000</v>
       </c>
       <c r="E35" s="3">
-        <v>37200</v>
+        <v>-126700</v>
       </c>
       <c r="F35" s="3">
-        <v>4200</v>
+        <v>37700</v>
       </c>
       <c r="G35" s="3">
-        <v>14700</v>
+        <v>4300</v>
       </c>
       <c r="H35" s="3">
-        <v>-206700</v>
+        <v>14900</v>
       </c>
       <c r="I35" s="3">
-        <v>-5100</v>
+        <v>-209600</v>
       </c>
       <c r="J35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K35" s="3">
         <v>3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>36500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2397,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>173400</v>
+        <v>120400</v>
       </c>
       <c r="E41" s="3">
-        <v>159400</v>
+        <v>175800</v>
       </c>
       <c r="F41" s="3">
-        <v>126400</v>
+        <v>161600</v>
       </c>
       <c r="G41" s="3">
-        <v>114700</v>
+        <v>128200</v>
       </c>
       <c r="H41" s="3">
-        <v>108900</v>
+        <v>116300</v>
       </c>
       <c r="I41" s="3">
-        <v>123000</v>
+        <v>110500</v>
       </c>
       <c r="J41" s="3">
+        <v>124800</v>
+      </c>
+      <c r="K41" s="3">
         <v>157100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>151800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>183300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>168400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>201400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>170500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>111100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>97700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>112800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>107000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2473,32 +2563,32 @@
       <c r="G42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="3">
-        <v>100</v>
+      <c r="H42" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="I42" s="3">
         <v>100</v>
       </c>
       <c r="J42" s="3">
+        <v>100</v>
+      </c>
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1200</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>35</v>
@@ -2509,368 +2599,389 @@
       <c r="S42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>101000</v>
+        <v>111600</v>
       </c>
       <c r="E43" s="3">
-        <v>93200</v>
+        <v>102400</v>
       </c>
       <c r="F43" s="3">
-        <v>91800</v>
+        <v>94600</v>
       </c>
       <c r="G43" s="3">
-        <v>107400</v>
+        <v>93100</v>
       </c>
       <c r="H43" s="3">
-        <v>93200</v>
+        <v>108900</v>
       </c>
       <c r="I43" s="3">
-        <v>88900</v>
+        <v>94500</v>
       </c>
       <c r="J43" s="3">
+        <v>90200</v>
+      </c>
+      <c r="K43" s="3">
         <v>100600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>123700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>105600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>93100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>107800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>98900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>43300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>61200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>156700</v>
+        <v>171600</v>
       </c>
       <c r="E44" s="3">
-        <v>179600</v>
+        <v>158900</v>
       </c>
       <c r="F44" s="3">
-        <v>142200</v>
+        <v>182100</v>
       </c>
       <c r="G44" s="3">
-        <v>121600</v>
+        <v>144200</v>
       </c>
       <c r="H44" s="3">
-        <v>124500</v>
+        <v>123300</v>
       </c>
       <c r="I44" s="3">
-        <v>111900</v>
+        <v>126300</v>
       </c>
       <c r="J44" s="3">
+        <v>113500</v>
+      </c>
+      <c r="K44" s="3">
         <v>116600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>125600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>115900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>96300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>72800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>45600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>16500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>17000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>19000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19900</v>
+        <v>24600</v>
       </c>
       <c r="E45" s="3">
-        <v>14700</v>
+        <v>20200</v>
       </c>
       <c r="F45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K45" s="3">
+        <v>14600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>13100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="N45" s="3">
+        <v>16500</v>
+      </c>
+      <c r="O45" s="3">
+        <v>10300</v>
+      </c>
+      <c r="P45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="S45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="T45" s="3">
         <v>11700</v>
       </c>
-      <c r="G45" s="3">
-        <v>14700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>14600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>13100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>12900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>16500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>10300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>8500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>10900</v>
-      </c>
-      <c r="S45" s="3">
-        <v>11700</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>451100</v>
+        <v>428200</v>
       </c>
       <c r="E46" s="3">
-        <v>446900</v>
+        <v>457400</v>
       </c>
       <c r="F46" s="3">
-        <v>372100</v>
+        <v>453200</v>
       </c>
       <c r="G46" s="3">
-        <v>358300</v>
+        <v>377400</v>
       </c>
       <c r="H46" s="3">
-        <v>342000</v>
+        <v>363300</v>
       </c>
       <c r="I46" s="3">
-        <v>340800</v>
+        <v>346800</v>
       </c>
       <c r="J46" s="3">
+        <v>345600</v>
+      </c>
+      <c r="K46" s="3">
         <v>389400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>414700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>379700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>389900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>353400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>388000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>320600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>182500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>168800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>181000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>195100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>162300</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>19400</v>
+        <v>26300</v>
       </c>
       <c r="E47" s="3">
-        <v>11400</v>
+        <v>19700</v>
       </c>
       <c r="F47" s="3">
-        <v>19700</v>
+        <v>11600</v>
       </c>
       <c r="G47" s="3">
-        <v>6800</v>
+        <v>19900</v>
       </c>
       <c r="H47" s="3">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="I47" s="3">
-        <v>6200</v>
+        <v>6600</v>
       </c>
       <c r="J47" s="3">
         <v>6300</v>
       </c>
       <c r="K47" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L47" s="3">
         <v>6500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>55300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>63700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>66000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>66600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>62800</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2130200</v>
+        <v>2150300</v>
       </c>
       <c r="E48" s="3">
-        <v>2247500</v>
+        <v>2160100</v>
       </c>
       <c r="F48" s="3">
-        <v>2237300</v>
+        <v>2279000</v>
       </c>
       <c r="G48" s="3">
-        <v>2202900</v>
+        <v>2268700</v>
       </c>
       <c r="H48" s="3">
-        <v>2121300</v>
+        <v>2233900</v>
       </c>
       <c r="I48" s="3">
-        <v>2341700</v>
+        <v>2151100</v>
       </c>
       <c r="J48" s="3">
+        <v>2374600</v>
+      </c>
+      <c r="K48" s="3">
         <v>2339100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2364800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2312900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2244400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1068000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1077700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1022500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1045000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>990100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>973400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>938900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>892600</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,52 +3163,55 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>62200</v>
+        <v>67400</v>
       </c>
       <c r="E52" s="3">
-        <v>63600</v>
+        <v>63100</v>
       </c>
       <c r="F52" s="3">
-        <v>65800</v>
+        <v>64500</v>
       </c>
       <c r="G52" s="3">
-        <v>65300</v>
+        <v>66700</v>
       </c>
       <c r="H52" s="3">
-        <v>69200</v>
+        <v>66200</v>
       </c>
       <c r="I52" s="3">
-        <v>61900</v>
+        <v>70100</v>
       </c>
       <c r="J52" s="3">
+        <v>62800</v>
+      </c>
+      <c r="K52" s="3">
         <v>52800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>44600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19700</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>35</v>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2662900</v>
+        <v>2672200</v>
       </c>
       <c r="E54" s="3">
-        <v>2769400</v>
+        <v>2700300</v>
       </c>
       <c r="F54" s="3">
-        <v>2694900</v>
+        <v>2808300</v>
       </c>
       <c r="G54" s="3">
-        <v>2633400</v>
+        <v>2732700</v>
       </c>
       <c r="H54" s="3">
-        <v>2538900</v>
+        <v>2670400</v>
       </c>
       <c r="I54" s="3">
-        <v>2750600</v>
+        <v>2574600</v>
       </c>
       <c r="J54" s="3">
+        <v>2789200</v>
+      </c>
+      <c r="K54" s="3">
         <v>2787600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2834100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2731000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2702900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1497700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1478200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1363900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1288500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1222500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1220500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1200600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1117800</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,362 +3399,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>135800</v>
+        <v>141200</v>
       </c>
       <c r="E57" s="3">
-        <v>106000</v>
+        <v>137800</v>
       </c>
       <c r="F57" s="3">
-        <v>100500</v>
+        <v>107500</v>
       </c>
       <c r="G57" s="3">
-        <v>102200</v>
+        <v>101900</v>
       </c>
       <c r="H57" s="3">
+        <v>103600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>99600</v>
+      </c>
+      <c r="J57" s="3">
         <v>98200</v>
       </c>
-      <c r="I57" s="3">
-        <v>96800</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>91300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>111500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>114200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>43300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>52600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>79600</v>
+        <v>80500</v>
       </c>
       <c r="E58" s="3">
-        <v>17300</v>
+        <v>80700</v>
       </c>
       <c r="F58" s="3">
-        <v>21100</v>
+        <v>17600</v>
       </c>
       <c r="G58" s="3">
-        <v>18000</v>
+        <v>21400</v>
       </c>
       <c r="H58" s="3">
-        <v>12700</v>
+        <v>18200</v>
       </c>
       <c r="I58" s="3">
+        <v>12900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K58" s="3">
         <v>13900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>13900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>14200</v>
       </c>
       <c r="L58" s="3">
         <v>14200</v>
       </c>
       <c r="M58" s="3">
+        <v>14200</v>
+      </c>
+      <c r="N58" s="3">
         <v>208500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>172500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>174400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>49000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>114400</v>
+        <v>116300</v>
       </c>
       <c r="E59" s="3">
-        <v>87500</v>
+        <v>116000</v>
       </c>
       <c r="F59" s="3">
+        <v>88800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>66900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>69200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>72900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>67100</v>
+      </c>
+      <c r="K59" s="3">
+        <v>66900</v>
+      </c>
+      <c r="L59" s="3">
+        <v>85700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>99600</v>
+      </c>
+      <c r="N59" s="3">
+        <v>82100</v>
+      </c>
+      <c r="O59" s="3">
+        <v>65600</v>
+      </c>
+      <c r="P59" s="3">
         <v>66000</v>
       </c>
-      <c r="G59" s="3">
-        <v>68200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>71800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>66200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>66900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>85700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>99600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>82100</v>
-      </c>
-      <c r="N59" s="3">
-        <v>65600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>66000</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>61400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>38700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>51300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>329900</v>
+        <v>337900</v>
       </c>
       <c r="E60" s="3">
-        <v>210900</v>
+        <v>334500</v>
       </c>
       <c r="F60" s="3">
-        <v>187600</v>
+        <v>213800</v>
       </c>
       <c r="G60" s="3">
-        <v>188300</v>
+        <v>190300</v>
       </c>
       <c r="H60" s="3">
-        <v>182800</v>
+        <v>191000</v>
       </c>
       <c r="I60" s="3">
-        <v>176900</v>
+        <v>185400</v>
       </c>
       <c r="J60" s="3">
+        <v>179400</v>
+      </c>
+      <c r="K60" s="3">
         <v>172200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>225300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>404900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>282000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>285900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>124600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>105500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>85700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>133100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>115100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>103300</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>278000</v>
+        <v>223300</v>
       </c>
       <c r="E61" s="3">
-        <v>388300</v>
+        <v>281900</v>
       </c>
       <c r="F61" s="3">
-        <v>437400</v>
+        <v>393700</v>
       </c>
       <c r="G61" s="3">
-        <v>382600</v>
+        <v>443500</v>
       </c>
       <c r="H61" s="3">
-        <v>312700</v>
+        <v>388000</v>
       </c>
       <c r="I61" s="3">
-        <v>294900</v>
+        <v>317100</v>
       </c>
       <c r="J61" s="3">
+        <v>299100</v>
+      </c>
+      <c r="K61" s="3">
         <v>316200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>295900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>238200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>87300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>71100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>71300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>221200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>190700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>185200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>217500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>207200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>312000</v>
+        <v>308700</v>
       </c>
       <c r="E62" s="3">
-        <v>301600</v>
+        <v>316400</v>
       </c>
       <c r="F62" s="3">
-        <v>303300</v>
+        <v>305800</v>
       </c>
       <c r="G62" s="3">
-        <v>303000</v>
+        <v>307600</v>
       </c>
       <c r="H62" s="3">
-        <v>299500</v>
+        <v>307300</v>
       </c>
       <c r="I62" s="3">
-        <v>330200</v>
+        <v>303700</v>
       </c>
       <c r="J62" s="3">
+        <v>334900</v>
+      </c>
+      <c r="K62" s="3">
         <v>334100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>335000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>336600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>302100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>79900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>80100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>70500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>69900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>65900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>63200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>69800</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>987200</v>
+        <v>942100</v>
       </c>
       <c r="E66" s="3">
-        <v>964800</v>
+        <v>1001000</v>
       </c>
       <c r="F66" s="3">
-        <v>989600</v>
+        <v>978400</v>
       </c>
       <c r="G66" s="3">
-        <v>934700</v>
+        <v>1003500</v>
       </c>
       <c r="H66" s="3">
-        <v>854500</v>
+        <v>947900</v>
       </c>
       <c r="I66" s="3">
-        <v>871900</v>
+        <v>866500</v>
       </c>
       <c r="J66" s="3">
+        <v>884200</v>
+      </c>
+      <c r="K66" s="3">
         <v>896500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>907200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>873600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>866400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>432400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>437200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>425900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>366600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>340700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>416500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>385600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>152600</v>
+        <v>191100</v>
       </c>
       <c r="E72" s="3">
-        <v>279000</v>
+        <v>154800</v>
       </c>
       <c r="F72" s="3">
-        <v>240800</v>
+        <v>282900</v>
       </c>
       <c r="G72" s="3">
-        <v>238400</v>
+        <v>244200</v>
       </c>
       <c r="H72" s="3">
-        <v>225100</v>
+        <v>241700</v>
       </c>
       <c r="I72" s="3">
-        <v>431300</v>
+        <v>228300</v>
       </c>
       <c r="J72" s="3">
+        <v>437400</v>
+      </c>
+      <c r="K72" s="3">
         <v>434900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>438800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>396200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>374300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>370600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>347500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>301700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>279700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>256000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>263400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>273600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>241300</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1675800</v>
+        <v>1730100</v>
       </c>
       <c r="E76" s="3">
-        <v>1804600</v>
+        <v>1699300</v>
       </c>
       <c r="F76" s="3">
-        <v>1705300</v>
+        <v>1830000</v>
       </c>
       <c r="G76" s="3">
-        <v>1698700</v>
+        <v>1729300</v>
       </c>
       <c r="H76" s="3">
-        <v>1684400</v>
+        <v>1722500</v>
       </c>
       <c r="I76" s="3">
-        <v>1878600</v>
+        <v>1708100</v>
       </c>
       <c r="J76" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1891100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1926800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1857400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1836500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1065400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1041000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>938000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>921900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>881800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>803900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>815000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>782700</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-124900</v>
+        <v>36000</v>
       </c>
       <c r="E81" s="3">
-        <v>37200</v>
+        <v>-126700</v>
       </c>
       <c r="F81" s="3">
-        <v>4200</v>
+        <v>37700</v>
       </c>
       <c r="G81" s="3">
-        <v>14700</v>
+        <v>4300</v>
       </c>
       <c r="H81" s="3">
-        <v>-206700</v>
+        <v>14900</v>
       </c>
       <c r="I81" s="3">
-        <v>-5100</v>
+        <v>-209600</v>
       </c>
       <c r="J81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K81" s="3">
         <v>3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>36500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>96900</v>
+        <v>69000</v>
       </c>
       <c r="E83" s="3">
-        <v>86500</v>
+        <v>98300</v>
       </c>
       <c r="F83" s="3">
-        <v>54000</v>
+        <v>87700</v>
       </c>
       <c r="G83" s="3">
-        <v>59900</v>
+        <v>54800</v>
       </c>
       <c r="H83" s="3">
-        <v>60200</v>
+        <v>60700</v>
       </c>
       <c r="I83" s="3">
-        <v>63400</v>
+        <v>61100</v>
       </c>
       <c r="J83" s="3">
+        <v>64300</v>
+      </c>
+      <c r="K83" s="3">
         <v>58100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>53000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>60500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>28400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>142200</v>
+        <v>67200</v>
       </c>
       <c r="E89" s="3">
-        <v>144100</v>
+        <v>144200</v>
       </c>
       <c r="F89" s="3">
-        <v>59000</v>
+        <v>146100</v>
       </c>
       <c r="G89" s="3">
-        <v>56500</v>
+        <v>59800</v>
       </c>
       <c r="H89" s="3">
-        <v>67100</v>
+        <v>57300</v>
       </c>
       <c r="I89" s="3">
-        <v>87500</v>
+        <v>68100</v>
       </c>
       <c r="J89" s="3">
+        <v>88700</v>
+      </c>
+      <c r="K89" s="3">
         <v>63200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>77100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>53200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>59300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-73300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-65000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-62100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-53800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-500</v>
       </c>
       <c r="Q91" s="3">
         <v>-500</v>
       </c>
       <c r="R91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-69000</v>
+        <v>-54200</v>
       </c>
       <c r="E94" s="3">
-        <v>-45600</v>
+        <v>-70000</v>
       </c>
       <c r="F94" s="3">
-        <v>-98300</v>
+        <v>-46200</v>
       </c>
       <c r="G94" s="3">
-        <v>-80600</v>
+        <v>-99600</v>
       </c>
       <c r="H94" s="3">
-        <v>-98500</v>
+        <v>-81800</v>
       </c>
       <c r="I94" s="3">
-        <v>-79800</v>
+        <v>-99900</v>
       </c>
       <c r="J94" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-78600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-90100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-69200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-70100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-26800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-46900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-58700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,181 +5792,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-61200</v>
+        <v>-66500</v>
       </c>
       <c r="E100" s="3">
-        <v>-63800</v>
+        <v>-62100</v>
       </c>
       <c r="F100" s="3">
-        <v>51000</v>
+        <v>-64700</v>
       </c>
       <c r="G100" s="3">
-        <v>29800</v>
+        <v>51700</v>
       </c>
       <c r="H100" s="3">
-        <v>15300</v>
+        <v>30200</v>
       </c>
       <c r="I100" s="3">
-        <v>-32000</v>
+        <v>15500</v>
       </c>
       <c r="J100" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="K100" s="3">
         <v>19000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>50600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-46600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>29100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>48800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>52900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1800</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2000</v>
       </c>
-      <c r="I101" s="3">
-        <v>-9800</v>
-      </c>
       <c r="J101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="K101" s="3">
         <v>4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
       </c>
       <c r="T101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U101" s="3">
         <v>-2500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14000</v>
+        <v>-55500</v>
       </c>
       <c r="E102" s="3">
-        <v>33000</v>
+        <v>14200</v>
       </c>
       <c r="F102" s="3">
-        <v>11800</v>
+        <v>33400</v>
       </c>
       <c r="G102" s="3">
-        <v>5700</v>
+        <v>11900</v>
       </c>
       <c r="H102" s="3">
-        <v>-14100</v>
+        <v>5800</v>
       </c>
       <c r="I102" s="3">
-        <v>-34100</v>
+        <v>-14300</v>
       </c>
       <c r="J102" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="K102" s="3">
         <v>7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>60400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>FVI</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>308600</v>
+        <v>353200</v>
       </c>
       <c r="E8" s="3">
-        <v>364000</v>
+        <v>305500</v>
       </c>
       <c r="F8" s="3">
-        <v>333600</v>
+        <v>360400</v>
       </c>
       <c r="G8" s="3">
-        <v>217400</v>
+        <v>330300</v>
       </c>
       <c r="H8" s="3">
-        <v>241100</v>
+        <v>215200</v>
       </c>
       <c r="I8" s="3">
-        <v>226000</v>
+        <v>238700</v>
       </c>
       <c r="J8" s="3">
+        <v>223700</v>
+      </c>
+      <c r="K8" s="3">
         <v>228600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>227200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>250800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>268700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>219500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>166600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>162900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>133800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>108800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>56700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>60500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>88500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>212700</v>
+        <v>244600</v>
       </c>
       <c r="E9" s="3">
-        <v>270700</v>
+        <v>210600</v>
       </c>
       <c r="F9" s="3">
-        <v>243100</v>
+        <v>268000</v>
       </c>
       <c r="G9" s="3">
-        <v>173400</v>
+        <v>240700</v>
       </c>
       <c r="H9" s="3">
-        <v>185600</v>
+        <v>171700</v>
       </c>
       <c r="I9" s="3">
-        <v>185100</v>
+        <v>183700</v>
       </c>
       <c r="J9" s="3">
+        <v>183200</v>
+      </c>
+      <c r="K9" s="3">
         <v>193200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>177700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>163400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>182700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>153100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>99600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>92100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>73100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>51200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>56700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>95900</v>
+        <v>108600</v>
       </c>
       <c r="E10" s="3">
-        <v>93300</v>
+        <v>94900</v>
       </c>
       <c r="F10" s="3">
-        <v>90400</v>
+        <v>92400</v>
       </c>
       <c r="G10" s="3">
-        <v>43900</v>
+        <v>89500</v>
       </c>
       <c r="H10" s="3">
-        <v>55500</v>
+        <v>43500</v>
       </c>
       <c r="I10" s="3">
-        <v>40900</v>
+        <v>54900</v>
       </c>
       <c r="J10" s="3">
+        <v>40500</v>
+      </c>
+      <c r="K10" s="3">
         <v>35400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>49500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>87300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>86000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>67000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>70800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>60600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>54800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>31800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,29 +988,29 @@
       <c r="F12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="3">
-        <v>800</v>
+      <c r="G12" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="H12" s="3">
+        <v>700</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="K12" s="3">
-        <v>700</v>
       </c>
       <c r="L12" s="3">
         <v>700</v>
       </c>
       <c r="M12" s="3">
+        <v>700</v>
+      </c>
+      <c r="N12" s="3">
         <v>600</v>
-      </c>
-      <c r="N12" s="3">
-        <v>300</v>
       </c>
       <c r="O12" s="3">
         <v>300</v>
@@ -1005,25 +1019,28 @@
         <v>300</v>
       </c>
       <c r="Q12" s="3">
+        <v>300</v>
+      </c>
+      <c r="R12" s="3">
         <v>700</v>
-      </c>
-      <c r="R12" s="3">
-        <v>200</v>
       </c>
       <c r="S12" s="3">
         <v>200</v>
       </c>
       <c r="T12" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>500</v>
       </c>
       <c r="V12" s="3">
+        <v>500</v>
+      </c>
+      <c r="W12" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1084,70 +1101,76 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="3">
-        <v>153800</v>
+      <c r="E14" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="F14" s="3">
+        <v>152200</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
-        <v>256600</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>254100</v>
+      </c>
+      <c r="K14" s="3">
         <v>6100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>17100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>244000</v>
+        <v>277900</v>
       </c>
       <c r="E17" s="3">
-        <v>470200</v>
+        <v>241600</v>
       </c>
       <c r="F17" s="3">
-        <v>271200</v>
+        <v>465500</v>
       </c>
       <c r="G17" s="3">
-        <v>206800</v>
+        <v>268500</v>
       </c>
       <c r="H17" s="3">
-        <v>208300</v>
+        <v>204700</v>
       </c>
       <c r="I17" s="3">
-        <v>463600</v>
+        <v>206200</v>
       </c>
       <c r="J17" s="3">
+        <v>458900</v>
+      </c>
+      <c r="K17" s="3">
         <v>220700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>209400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>194800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>217000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>204300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>122000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>107100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>97300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>71700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>58200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>76900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>80500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>64600</v>
+        <v>75300</v>
       </c>
       <c r="E18" s="3">
-        <v>-106200</v>
+        <v>64000</v>
       </c>
       <c r="F18" s="3">
-        <v>62300</v>
+        <v>-105100</v>
       </c>
       <c r="G18" s="3">
-        <v>10600</v>
+        <v>61700</v>
       </c>
       <c r="H18" s="3">
-        <v>32800</v>
+        <v>10500</v>
       </c>
       <c r="I18" s="3">
-        <v>-237600</v>
+        <v>32500</v>
       </c>
       <c r="J18" s="3">
+        <v>-235200</v>
+      </c>
+      <c r="K18" s="3">
         <v>7900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>56000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>51600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>44700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>55800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1377,318 +1410,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>3200</v>
+        <v>2600</v>
       </c>
       <c r="E20" s="3">
-        <v>7700</v>
+        <v>3100</v>
       </c>
       <c r="F20" s="3">
-        <v>-9400</v>
+        <v>7600</v>
       </c>
       <c r="G20" s="3">
-        <v>-3100</v>
+        <v>-9300</v>
       </c>
       <c r="H20" s="3">
-        <v>-4800</v>
+        <v>-3000</v>
       </c>
       <c r="I20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>136700</v>
+        <v>155700</v>
       </c>
       <c r="E21" s="3">
+        <v>135400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
-        <v>140600</v>
-      </c>
       <c r="G21" s="3">
-        <v>62300</v>
+        <v>139200</v>
       </c>
       <c r="H21" s="3">
-        <v>88800</v>
+        <v>61700</v>
       </c>
       <c r="I21" s="3">
-        <v>-178500</v>
+        <v>87900</v>
       </c>
       <c r="J21" s="3">
+        <v>-176700</v>
+      </c>
+      <c r="K21" s="3">
         <v>66700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>79600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>100200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>105900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>67300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>69700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>84400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>54900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>51200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>8000</v>
+        <v>8600</v>
       </c>
       <c r="E22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F22" s="3">
         <v>1400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>800</v>
       </c>
       <c r="M22" s="3">
+        <v>800</v>
+      </c>
+      <c r="N22" s="3">
         <v>4600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1300</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
       </c>
       <c r="T22" s="3">
+        <v>200</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>59800</v>
+        <v>69300</v>
       </c>
       <c r="E23" s="3">
-        <v>-99900</v>
+        <v>59200</v>
       </c>
       <c r="F23" s="3">
-        <v>51400</v>
+        <v>-98900</v>
       </c>
       <c r="G23" s="3">
-        <v>6200</v>
+        <v>50900</v>
       </c>
       <c r="H23" s="3">
-        <v>27200</v>
+        <v>6100</v>
       </c>
       <c r="I23" s="3">
-        <v>-241200</v>
+        <v>26900</v>
       </c>
       <c r="J23" s="3">
+        <v>-238800</v>
+      </c>
+      <c r="K23" s="3">
         <v>2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>40800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>39000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>54900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>25700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>19900</v>
+        <v>10400</v>
       </c>
       <c r="E24" s="3">
-        <v>23400</v>
+        <v>19700</v>
       </c>
       <c r="F24" s="3">
+        <v>23100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>8900</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>10800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="K24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L24" s="3">
+        <v>18400</v>
+      </c>
+      <c r="M24" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="O24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>16700</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>18400</v>
+      </c>
+      <c r="R24" s="3">
+        <v>11800</v>
+      </c>
+      <c r="S24" s="3">
+        <v>19500</v>
+      </c>
+      <c r="T24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="U24" s="3">
         <v>9000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3">
-        <v>10900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="W24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
-        <v>18400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>9300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>18300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>12000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>16700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>18400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>11800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>19500</v>
-      </c>
-      <c r="S24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="T24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V24" s="3">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>39900</v>
+        <v>58900</v>
       </c>
       <c r="E26" s="3">
-        <v>-123300</v>
+        <v>39500</v>
       </c>
       <c r="F26" s="3">
-        <v>42400</v>
+        <v>-122000</v>
       </c>
       <c r="G26" s="3">
-        <v>4800</v>
+        <v>42000</v>
       </c>
       <c r="H26" s="3">
-        <v>16300</v>
+        <v>4700</v>
       </c>
       <c r="I26" s="3">
-        <v>-220100</v>
+        <v>16100</v>
       </c>
       <c r="J26" s="3">
+        <v>-217900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>22400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>36000</v>
+        <v>55200</v>
       </c>
       <c r="E27" s="3">
-        <v>-126700</v>
+        <v>35700</v>
       </c>
       <c r="F27" s="3">
-        <v>37700</v>
+        <v>-125400</v>
       </c>
       <c r="G27" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H27" s="3">
         <v>4300</v>
       </c>
-      <c r="H27" s="3">
-        <v>14900</v>
-      </c>
       <c r="I27" s="3">
-        <v>-209600</v>
+        <v>14800</v>
       </c>
       <c r="J27" s="3">
+        <v>-207500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>22400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-3200</v>
+        <v>-2600</v>
       </c>
       <c r="E32" s="3">
-        <v>-7700</v>
+        <v>-3100</v>
       </c>
       <c r="F32" s="3">
-        <v>9400</v>
+        <v>-7600</v>
       </c>
       <c r="G32" s="3">
-        <v>3100</v>
+        <v>9300</v>
       </c>
       <c r="H32" s="3">
-        <v>4800</v>
+        <v>3000</v>
       </c>
       <c r="I32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>36000</v>
+        <v>55200</v>
       </c>
       <c r="E33" s="3">
-        <v>-126700</v>
+        <v>35700</v>
       </c>
       <c r="F33" s="3">
-        <v>37700</v>
+        <v>-125400</v>
       </c>
       <c r="G33" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H33" s="3">
         <v>4300</v>
       </c>
-      <c r="H33" s="3">
-        <v>14900</v>
-      </c>
       <c r="I33" s="3">
-        <v>-209600</v>
+        <v>14800</v>
       </c>
       <c r="J33" s="3">
+        <v>-207500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>22400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>36000</v>
+        <v>55200</v>
       </c>
       <c r="E35" s="3">
-        <v>-126700</v>
+        <v>35700</v>
       </c>
       <c r="F35" s="3">
-        <v>37700</v>
+        <v>-125400</v>
       </c>
       <c r="G35" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H35" s="3">
         <v>4300</v>
       </c>
-      <c r="H35" s="3">
-        <v>14900</v>
-      </c>
       <c r="I35" s="3">
-        <v>-209600</v>
+        <v>14800</v>
       </c>
       <c r="J35" s="3">
+        <v>-207500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>22400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>120400</v>
+        <v>143500</v>
       </c>
       <c r="E41" s="3">
-        <v>175800</v>
+        <v>119200</v>
       </c>
       <c r="F41" s="3">
-        <v>161600</v>
+        <v>174100</v>
       </c>
       <c r="G41" s="3">
-        <v>128200</v>
+        <v>160000</v>
       </c>
       <c r="H41" s="3">
-        <v>116300</v>
+        <v>126900</v>
       </c>
       <c r="I41" s="3">
-        <v>110500</v>
+        <v>115100</v>
       </c>
       <c r="J41" s="3">
+        <v>109300</v>
+      </c>
+      <c r="K41" s="3">
         <v>124800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>157100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>151800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>144700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>183300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>168400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>201400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>170500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>111100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>97700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>107000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2566,32 +2656,32 @@
       <c r="H42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I42" s="3">
-        <v>100</v>
+      <c r="I42" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="J42" s="3">
         <v>100</v>
       </c>
       <c r="K42" s="3">
+        <v>100</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>35</v>
@@ -2602,386 +2692,407 @@
       <c r="T42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>111600</v>
+        <v>114600</v>
       </c>
       <c r="E43" s="3">
-        <v>102400</v>
+        <v>110500</v>
       </c>
       <c r="F43" s="3">
-        <v>94600</v>
+        <v>101400</v>
       </c>
       <c r="G43" s="3">
+        <v>93600</v>
+      </c>
+      <c r="H43" s="3">
+        <v>92200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>107800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>93600</v>
+      </c>
+      <c r="K43" s="3">
+        <v>90200</v>
+      </c>
+      <c r="L43" s="3">
+        <v>100600</v>
+      </c>
+      <c r="M43" s="3">
+        <v>123700</v>
+      </c>
+      <c r="N43" s="3">
+        <v>105600</v>
+      </c>
+      <c r="O43" s="3">
         <v>93100</v>
       </c>
-      <c r="H43" s="3">
-        <v>108900</v>
-      </c>
-      <c r="I43" s="3">
-        <v>94500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>90200</v>
-      </c>
-      <c r="K43" s="3">
-        <v>100600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>123700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>105600</v>
-      </c>
-      <c r="N43" s="3">
-        <v>93100</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>107800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>98900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>43300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>61200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>43400</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>171600</v>
+        <v>177400</v>
       </c>
       <c r="E44" s="3">
-        <v>158900</v>
+        <v>169900</v>
       </c>
       <c r="F44" s="3">
-        <v>182100</v>
+        <v>157300</v>
       </c>
       <c r="G44" s="3">
-        <v>144200</v>
+        <v>180300</v>
       </c>
       <c r="H44" s="3">
-        <v>123300</v>
+        <v>142700</v>
       </c>
       <c r="I44" s="3">
-        <v>126300</v>
+        <v>122100</v>
       </c>
       <c r="J44" s="3">
+        <v>125000</v>
+      </c>
+      <c r="K44" s="3">
         <v>113500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>116600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>125600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>115900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>96300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>72800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>45600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>16500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>17000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>19000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>18600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>24600</v>
+        <v>86300</v>
       </c>
       <c r="E45" s="3">
-        <v>20200</v>
+        <v>24300</v>
       </c>
       <c r="F45" s="3">
-        <v>14900</v>
+        <v>20000</v>
       </c>
       <c r="G45" s="3">
-        <v>11900</v>
+        <v>14700</v>
       </c>
       <c r="H45" s="3">
-        <v>14900</v>
+        <v>11800</v>
       </c>
       <c r="I45" s="3">
-        <v>15400</v>
+        <v>14700</v>
       </c>
       <c r="J45" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K45" s="3">
         <v>17000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>428200</v>
+        <v>521800</v>
       </c>
       <c r="E46" s="3">
-        <v>457400</v>
+        <v>423900</v>
       </c>
       <c r="F46" s="3">
-        <v>453200</v>
+        <v>452800</v>
       </c>
       <c r="G46" s="3">
-        <v>377400</v>
+        <v>448700</v>
       </c>
       <c r="H46" s="3">
-        <v>363300</v>
+        <v>373600</v>
       </c>
       <c r="I46" s="3">
-        <v>346800</v>
+        <v>359700</v>
       </c>
       <c r="J46" s="3">
+        <v>343300</v>
+      </c>
+      <c r="K46" s="3">
         <v>345600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>389400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>414700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>379700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>389900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>353400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>388000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>320600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>182500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>168800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>181000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>195100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>162300</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>26300</v>
+        <v>32300</v>
       </c>
       <c r="E47" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>19500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H47" s="3">
         <v>19700</v>
       </c>
-      <c r="F47" s="3">
-        <v>11600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>19900</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6900</v>
       </c>
-      <c r="I47" s="3">
-        <v>6600</v>
-      </c>
       <c r="J47" s="3">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="K47" s="3">
         <v>6300</v>
       </c>
       <c r="L47" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M47" s="3">
         <v>6500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>24000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>55300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>61100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>63700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>66000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>66600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>62800</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2150300</v>
+        <v>2119000</v>
       </c>
       <c r="E48" s="3">
-        <v>2160100</v>
+        <v>2128900</v>
       </c>
       <c r="F48" s="3">
-        <v>2279000</v>
+        <v>2138600</v>
       </c>
       <c r="G48" s="3">
-        <v>2268700</v>
+        <v>2256300</v>
       </c>
       <c r="H48" s="3">
-        <v>2233900</v>
+        <v>2246100</v>
       </c>
       <c r="I48" s="3">
-        <v>2151100</v>
+        <v>2211600</v>
       </c>
       <c r="J48" s="3">
+        <v>2129600</v>
+      </c>
+      <c r="K48" s="3">
         <v>2374600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2339100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2364800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2312900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2244400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1068000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1077700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1022500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1045000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>990100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>973400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>938900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>892600</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,55 +3283,58 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>67400</v>
+        <v>77700</v>
       </c>
       <c r="E52" s="3">
-        <v>63100</v>
+        <v>66700</v>
       </c>
       <c r="F52" s="3">
-        <v>64500</v>
+        <v>62500</v>
       </c>
       <c r="G52" s="3">
-        <v>66700</v>
+        <v>63900</v>
       </c>
       <c r="H52" s="3">
-        <v>66200</v>
+        <v>66000</v>
       </c>
       <c r="I52" s="3">
-        <v>70100</v>
+        <v>65600</v>
       </c>
       <c r="J52" s="3">
+        <v>69400</v>
+      </c>
+      <c r="K52" s="3">
         <v>62800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>52800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>44600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19700</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>35</v>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2672200</v>
+        <v>2750700</v>
       </c>
       <c r="E54" s="3">
-        <v>2700300</v>
+        <v>2645500</v>
       </c>
       <c r="F54" s="3">
-        <v>2808300</v>
+        <v>2673300</v>
       </c>
       <c r="G54" s="3">
-        <v>2732700</v>
+        <v>2780300</v>
       </c>
       <c r="H54" s="3">
-        <v>2670400</v>
+        <v>2705500</v>
       </c>
       <c r="I54" s="3">
-        <v>2574600</v>
+        <v>2643700</v>
       </c>
       <c r="J54" s="3">
+        <v>2548900</v>
+      </c>
+      <c r="K54" s="3">
         <v>2789200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2787600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2834100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2731000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2702900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1497700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1478200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1363900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1288500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1222500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1220500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1200600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1117800</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,380 +3530,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>141200</v>
+        <v>132000</v>
       </c>
       <c r="E57" s="3">
-        <v>137800</v>
+        <v>139700</v>
       </c>
       <c r="F57" s="3">
-        <v>107500</v>
+        <v>136400</v>
       </c>
       <c r="G57" s="3">
-        <v>101900</v>
+        <v>106400</v>
       </c>
       <c r="H57" s="3">
-        <v>103600</v>
+        <v>100900</v>
       </c>
       <c r="I57" s="3">
-        <v>99600</v>
+        <v>102600</v>
       </c>
       <c r="J57" s="3">
+        <v>98600</v>
+      </c>
+      <c r="K57" s="3">
         <v>98200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>91300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>111500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>114200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>38300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>43300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>52600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>80500</v>
+        <v>80700</v>
       </c>
       <c r="E58" s="3">
-        <v>80700</v>
+        <v>79700</v>
       </c>
       <c r="F58" s="3">
-        <v>17600</v>
+        <v>79900</v>
       </c>
       <c r="G58" s="3">
-        <v>21400</v>
+        <v>17400</v>
       </c>
       <c r="H58" s="3">
-        <v>18200</v>
+        <v>21200</v>
       </c>
       <c r="I58" s="3">
-        <v>12900</v>
+        <v>18000</v>
       </c>
       <c r="J58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K58" s="3">
         <v>14100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>14200</v>
       </c>
       <c r="M58" s="3">
         <v>14200</v>
       </c>
       <c r="N58" s="3">
+        <v>14200</v>
+      </c>
+      <c r="O58" s="3">
         <v>208500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>172500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>174400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>49000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>116300</v>
+        <v>132100</v>
       </c>
       <c r="E59" s="3">
-        <v>116000</v>
+        <v>115100</v>
       </c>
       <c r="F59" s="3">
-        <v>88800</v>
+        <v>114800</v>
       </c>
       <c r="G59" s="3">
+        <v>87900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>66300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>68500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>72100</v>
+      </c>
+      <c r="K59" s="3">
+        <v>67100</v>
+      </c>
+      <c r="L59" s="3">
         <v>66900</v>
       </c>
-      <c r="H59" s="3">
-        <v>69200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>72900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>67100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>66900</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>85700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>99600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>82100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>65600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>66000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>61400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>38700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>40900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>51300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36800</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>337900</v>
+        <v>344700</v>
       </c>
       <c r="E60" s="3">
         <v>334500</v>
       </c>
       <c r="F60" s="3">
-        <v>213800</v>
+        <v>331200</v>
       </c>
       <c r="G60" s="3">
-        <v>190300</v>
+        <v>211700</v>
       </c>
       <c r="H60" s="3">
-        <v>191000</v>
+        <v>188400</v>
       </c>
       <c r="I60" s="3">
-        <v>185400</v>
+        <v>189100</v>
       </c>
       <c r="J60" s="3">
+        <v>183500</v>
+      </c>
+      <c r="K60" s="3">
         <v>179400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>172200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>225300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>404900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>282000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>285900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>124600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>105500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>85700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>133100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>115100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>103300</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>223300</v>
+        <v>223800</v>
       </c>
       <c r="E61" s="3">
-        <v>281900</v>
+        <v>221100</v>
       </c>
       <c r="F61" s="3">
-        <v>393700</v>
+        <v>279000</v>
       </c>
       <c r="G61" s="3">
-        <v>443500</v>
+        <v>389800</v>
       </c>
       <c r="H61" s="3">
-        <v>388000</v>
+        <v>439100</v>
       </c>
       <c r="I61" s="3">
-        <v>317100</v>
+        <v>384100</v>
       </c>
       <c r="J61" s="3">
+        <v>314000</v>
+      </c>
+      <c r="K61" s="3">
         <v>299100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>316200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>295900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>238200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>87300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>71100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>71300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>221200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>190700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>185200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>217500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>207200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>308700</v>
+        <v>293600</v>
       </c>
       <c r="E62" s="3">
-        <v>316400</v>
+        <v>305600</v>
       </c>
       <c r="F62" s="3">
-        <v>305800</v>
+        <v>313200</v>
       </c>
       <c r="G62" s="3">
-        <v>307600</v>
+        <v>302800</v>
       </c>
       <c r="H62" s="3">
-        <v>307300</v>
+        <v>304500</v>
       </c>
       <c r="I62" s="3">
-        <v>303700</v>
+        <v>304200</v>
       </c>
       <c r="J62" s="3">
+        <v>300700</v>
+      </c>
+      <c r="K62" s="3">
         <v>334900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>334100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>335000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>336600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>302100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>79300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>80100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>70500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>69900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>65900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>63200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>69800</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>942100</v>
+        <v>937300</v>
       </c>
       <c r="E66" s="3">
-        <v>1001000</v>
+        <v>932700</v>
       </c>
       <c r="F66" s="3">
-        <v>978400</v>
+        <v>991000</v>
       </c>
       <c r="G66" s="3">
-        <v>1003500</v>
+        <v>968600</v>
       </c>
       <c r="H66" s="3">
-        <v>947900</v>
+        <v>993400</v>
       </c>
       <c r="I66" s="3">
-        <v>866500</v>
+        <v>938400</v>
       </c>
       <c r="J66" s="3">
+        <v>857800</v>
+      </c>
+      <c r="K66" s="3">
         <v>884200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>896500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>907200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>873600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>866400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>432400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>437200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>425900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>366600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>340700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>416500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>385600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>191100</v>
+        <v>242900</v>
       </c>
       <c r="E72" s="3">
-        <v>154800</v>
+        <v>189200</v>
       </c>
       <c r="F72" s="3">
-        <v>282900</v>
+        <v>153200</v>
       </c>
       <c r="G72" s="3">
-        <v>244200</v>
+        <v>280000</v>
       </c>
       <c r="H72" s="3">
         <v>241700</v>
       </c>
       <c r="I72" s="3">
-        <v>228300</v>
+        <v>239300</v>
       </c>
       <c r="J72" s="3">
+        <v>226000</v>
+      </c>
+      <c r="K72" s="3">
         <v>437400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>434900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>438800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>396200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>374300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>370600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>347500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>301700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>279700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>256000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>263400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>273600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>241300</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1730100</v>
+        <v>1813500</v>
       </c>
       <c r="E76" s="3">
-        <v>1699300</v>
+        <v>1712900</v>
       </c>
       <c r="F76" s="3">
-        <v>1830000</v>
+        <v>1682300</v>
       </c>
       <c r="G76" s="3">
-        <v>1729300</v>
+        <v>1811700</v>
       </c>
       <c r="H76" s="3">
-        <v>1722500</v>
+        <v>1712000</v>
       </c>
       <c r="I76" s="3">
-        <v>1708100</v>
+        <v>1705300</v>
       </c>
       <c r="J76" s="3">
+        <v>1691000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1905000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1891100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1926800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1857400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1836500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1065400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1041000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>938000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>921900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>881800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>803900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>815000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>782700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>36000</v>
+        <v>55200</v>
       </c>
       <c r="E81" s="3">
-        <v>-126700</v>
+        <v>35700</v>
       </c>
       <c r="F81" s="3">
-        <v>37700</v>
+        <v>-125400</v>
       </c>
       <c r="G81" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H81" s="3">
         <v>4300</v>
       </c>
-      <c r="H81" s="3">
-        <v>14900</v>
-      </c>
       <c r="I81" s="3">
-        <v>-209600</v>
+        <v>14800</v>
       </c>
       <c r="J81" s="3">
+        <v>-207500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>22400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>69000</v>
+        <v>77800</v>
       </c>
       <c r="E83" s="3">
-        <v>98300</v>
+        <v>68300</v>
       </c>
       <c r="F83" s="3">
-        <v>87700</v>
+        <v>97300</v>
       </c>
       <c r="G83" s="3">
-        <v>54800</v>
+        <v>86900</v>
       </c>
       <c r="H83" s="3">
-        <v>60700</v>
+        <v>54200</v>
       </c>
       <c r="I83" s="3">
-        <v>61100</v>
+        <v>60100</v>
       </c>
       <c r="J83" s="3">
+        <v>60500</v>
+      </c>
+      <c r="K83" s="3">
         <v>64300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>58100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>53000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>60500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>28400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>67200</v>
+        <v>99900</v>
       </c>
       <c r="E89" s="3">
-        <v>144200</v>
+        <v>66500</v>
       </c>
       <c r="F89" s="3">
-        <v>146100</v>
+        <v>142700</v>
       </c>
       <c r="G89" s="3">
-        <v>59800</v>
+        <v>144600</v>
       </c>
       <c r="H89" s="3">
-        <v>57300</v>
+        <v>59200</v>
       </c>
       <c r="I89" s="3">
-        <v>68100</v>
+        <v>56700</v>
       </c>
       <c r="J89" s="3">
+        <v>67400</v>
+      </c>
+      <c r="K89" s="3">
         <v>88700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>63200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>45700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>77100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>53200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>40400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>59300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-41300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-61600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-73300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-62100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-53800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
       </c>
       <c r="R91" s="3">
         <v>-500</v>
       </c>
       <c r="S91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-54200</v>
+        <v>-64000</v>
       </c>
       <c r="E94" s="3">
-        <v>-70000</v>
+        <v>-53700</v>
       </c>
       <c r="F94" s="3">
-        <v>-46200</v>
+        <v>-69300</v>
       </c>
       <c r="G94" s="3">
-        <v>-99600</v>
+        <v>-45800</v>
       </c>
       <c r="H94" s="3">
-        <v>-81800</v>
+        <v>-98700</v>
       </c>
       <c r="I94" s="3">
-        <v>-99900</v>
+        <v>-81000</v>
       </c>
       <c r="J94" s="3">
+        <v>-98900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-80900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-78600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-90100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-69200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-70100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-42000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-46900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-58700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-80100</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-66500</v>
+        <v>-12800</v>
       </c>
       <c r="E100" s="3">
-        <v>-62100</v>
+        <v>-65800</v>
       </c>
       <c r="F100" s="3">
-        <v>-64700</v>
+        <v>-61500</v>
       </c>
       <c r="G100" s="3">
-        <v>51700</v>
+        <v>-64000</v>
       </c>
       <c r="H100" s="3">
-        <v>30200</v>
+        <v>51200</v>
       </c>
       <c r="I100" s="3">
-        <v>15500</v>
+        <v>29900</v>
       </c>
       <c r="J100" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-32500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>19000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>50600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-46600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>29100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>52900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
       </c>
       <c r="U101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V101" s="3">
         <v>-2500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-55500</v>
+        <v>24300</v>
       </c>
       <c r="E102" s="3">
-        <v>14200</v>
+        <v>-54900</v>
       </c>
       <c r="F102" s="3">
-        <v>33400</v>
+        <v>14100</v>
       </c>
       <c r="G102" s="3">
-        <v>11900</v>
+        <v>33100</v>
       </c>
       <c r="H102" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I102" s="3">
         <v>5800</v>
       </c>
-      <c r="I102" s="3">
-        <v>-14300</v>
-      </c>
       <c r="J102" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-34600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-33000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>60400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6500</v>
       </c>
     </row>
